--- a/PPREstimation/output/top10/36_2_South_China_Sea_SCS-2007_Northern_South_China_Sea_(1970s).xlsx
+++ b/PPREstimation/output/top10/36_2_South_China_Sea_SCS-2007_Northern_South_China_Sea_(1970s).xlsx
@@ -701,7 +701,11 @@
           <t>DET</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Non-living detritus.</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
       </c>
@@ -785,7 +789,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Marine turtles; no species list documented.</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="n">
         <v>2.972461641294619</v>
       </c>
@@ -869,7 +877,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Other marine mammals; no species list documented.</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="n">
         <v>3.922805246334676</v>
       </c>
@@ -953,7 +965,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Pinnipeds; no species list documented.</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="n">
         <v>4.146384704092291</v>
       </c>
@@ -1037,7 +1053,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Seabirds; no species list documented.</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="n">
         <v>3.414700950377541</v>
       </c>
@@ -1121,7 +1141,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Pelagic elasmobranchs. No species list documented.</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="n">
         <v>3.989708938669605</v>
       </c>
@@ -1205,7 +1229,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Demersal elasmobranchs. No species list documented.</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="n">
         <v>3.509427430945212</v>
       </c>
@@ -1289,7 +1317,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Pelagic fish with maximum total length &gt;30 cm, adult stanza from 18 months; includes scombrids.</t>
+        </is>
+      </c>
       <c r="F10" s="2" t="n">
         <v>3.367201063009562</v>
       </c>
@@ -1373,7 +1405,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Pelagic fish with maximum total length &gt;30 cm, juvenile stanza; source paragraph mistakenly says demersal, but heading, examples and stanza names establish pelagic.</t>
+        </is>
+      </c>
       <c r="F11" s="2" t="n">
         <v>2.893396853714223</v>
       </c>
@@ -1457,7 +1493,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Pelagic fish with maximum total length &lt;=30 cm, including sardines, thryssa and anchovies.</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="n">
         <v>2.781666666666666</v>
       </c>
@@ -1541,7 +1581,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Psenopsis anomala; definition: Psenopsis anomala.</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="n">
         <v>3.03486548350679</v>
       </c>
@@ -1625,7 +1669,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Final table has one Benthopelagic fish group. Appendix separately describes small &lt;=30 cm and large &gt;30 cm benthopelagic fish; their relationship to the final single pool is not resolved.</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="n">
         <v>2.780602456126404</v>
       </c>
@@ -1709,7 +1757,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Demersal fish with maximum total length &gt;30 cm, adult stanza from 18 months; dedicated groups excluded.</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="n">
         <v>3.427086988746579</v>
       </c>
@@ -1793,7 +1845,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Demersal fish with maximum total length &gt;30 cm, juvenile stanza; dedicated groups excluded.</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="n">
         <v>3.043612179667134</v>
       </c>
@@ -1877,7 +1933,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Demersal fish with maximum total length &lt;=30 cm, except taxa in dedicated groups.</t>
+        </is>
+      </c>
       <c r="F17" s="2" t="n">
         <v>3.00931693541396</v>
       </c>
@@ -1961,7 +2021,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Larimichthys crocea; definition: Large Sciaenidae &gt;30 cm maximum length, adult fish from 24 months.</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="n">
         <v>3.472838939946794</v>
       </c>
@@ -2045,7 +2109,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Larimichthys crocea; definition: Large Sciaenidae &gt;30 cm maximum length, immature fish younger than 24 months.</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="n">
         <v>3.238588184699975</v>
       </c>
@@ -2129,7 +2197,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Agyrosomus spp.; Pennahia spp.; Pennahia (Agyrosomus) argentatus; definition: Small Sciaenidae &lt;=30 cm; Pennahia is explicitly listed despite differing SAU size classes.</t>
+        </is>
+      </c>
       <c r="F20" s="2" t="n">
         <v>3.312753045334324</v>
       </c>
@@ -2213,7 +2285,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Family Serranidae; the final table calls this Adult groupers but supplies no separate juvenile grouper compartment.</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="n">
         <v>3.759047426500872</v>
       </c>
@@ -2297,7 +2373,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Family Lutjanidae.</t>
+        </is>
+      </c>
       <c r="F22" s="2" t="n">
         <v>3.769209176753436</v>
       </c>
@@ -2381,7 +2461,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Family Stromateidae. Other pomfret-like families are excluded from the stated taxonomic definition.</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="n">
         <v>3.587017325582895</v>
       </c>
@@ -2465,7 +2549,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Trichiurus lepturus; definition: Family Trichiuridae, adult stanza from 18 months.</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="n">
         <v>3.913681634309746</v>
       </c>
@@ -2549,7 +2637,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Trichiurus lepturus; definition: Family Trichiuridae, juvenile stanza younger than 18 months.</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="n">
         <v>3.878329620318159</v>
       </c>
@@ -2633,7 +2725,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Saurida tumbil; S. undosquamis; definition: Family Synodontidae.</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="n">
         <v>3.856614847729229</v>
       </c>
@@ -2717,7 +2813,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Family Priacanthidae.</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="n">
         <v>3.471984562385465</v>
       </c>
@@ -2801,7 +2901,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Nemipterus virgatus; N. bathybius; N. japonicus; definition: Family Nemipteridae.</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="n">
         <v>3.210667554973283</v>
       </c>
@@ -2885,7 +2989,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Loligo edulis; L. chinensis; definition: Cephalopoda, dominated by Loligo squid.</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="n">
         <v>3.29081348223872</v>
       </c>
@@ -2969,7 +3077,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Crabs.</t>
+        </is>
+      </c>
       <c r="F30" s="2" t="n">
         <v>2.523917480221986</v>
       </c>
@@ -3053,7 +3165,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Metapenaeopsis palmensis; M. barbata; definition: Shrimps including penaeids; Acetes is explicitly in Zooplankton.</t>
+        </is>
+      </c>
       <c r="F31" s="2" t="n">
         <v>2.314</v>
       </c>
@@ -3137,7 +3253,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Sessile and other invertebrates, separate from polychaetes, echinoderms, crustaceans and molluscs.</t>
+        </is>
+      </c>
       <c r="F32" s="2" t="n">
         <v>2.6</v>
       </c>
@@ -3221,7 +3341,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Non-cephalopod Mollusca.</t>
+        </is>
+      </c>
       <c r="F33" s="2" t="n">
         <v>2.177777777777778</v>
       </c>
@@ -3305,7 +3429,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Benthic crustaceans excluding shrimps and crabs; Oratosquilla spp. supplies the P/B estimate.</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="n">
         <v>2.199822222222222</v>
       </c>
@@ -3389,7 +3517,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Echinodermata.</t>
+        </is>
+      </c>
       <c r="F35" s="2" t="n">
         <v>2.333214688865273</v>
       </c>
@@ -3473,7 +3605,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Polychaeta.</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="n">
         <v>2</v>
       </c>
@@ -3557,7 +3693,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Medusae of Cnidaria.</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="n">
         <v>3.104070721217805</v>
       </c>
@@ -3641,7 +3781,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Acetes spp.; definition: Zooplankton; explicitly includes the landed Mo shrimp Acetes spp.</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="n">
         <v>2</v>
       </c>
@@ -3725,7 +3869,11 @@
           <t>PP</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Benthic algae.</t>
+        </is>
+      </c>
       <c r="F39" s="2" t="n">
         <v>1</v>
       </c>
@@ -3809,7 +3957,11 @@
           <t>PP</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Phytoplankton dominated by diatoms, followed by dinoflagellates.</t>
+        </is>
+      </c>
       <c r="F40" s="2" t="n">
         <v>1</v>
       </c>
@@ -4204,10 +4356,10 @@
         <v>218.2903672637023</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>539.6555435687844</v>
+        <v>552.8286920932502</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>111935.0453314855</v>
+        <v>117845.4613958489</v>
       </c>
     </row>
     <row r="5">
@@ -4268,10 +4420,10 @@
         <v>1087.971074959602</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>2603.514843046855</v>
+        <v>2656.829874710661</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>1925132.942959693</v>
+        <v>1977457.18367944</v>
       </c>
     </row>
     <row r="6">
@@ -4332,10 +4484,10 @@
         <v>3369.904771901306</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>8521.353907836708</v>
+        <v>8758.355410165243</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>506186.0623969175</v>
+        <v>520820.5319576079</v>
       </c>
     </row>
     <row r="7">
@@ -4396,10 +4548,10 @@
         <v>6369.180946079377</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>14726.88071274857</v>
+        <v>15316.03198880676</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>104799513.7996604</v>
+        <v>105868755.5056871</v>
       </c>
     </row>
     <row r="8">
@@ -4460,10 +4612,10 @@
         <v>57.05381350046034</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>136.836114578961</v>
+        <v>139.1985980320612</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>125081.396857108</v>
+        <v>127625.7634441447</v>
       </c>
     </row>
     <row r="9">
@@ -4524,10 +4676,10 @@
         <v>24.76611884682158</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>60.69965276997078</v>
+        <v>61.46270918557458</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>13703.8279994188</v>
+        <v>13974.15801482531</v>
       </c>
     </row>
     <row r="10">
@@ -4588,10 +4740,10 @@
         <v>35.07423985085238</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>66.02494688679417</v>
+        <v>70.29519099158354</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>6059.102662189597</v>
+        <v>6298.948576694078</v>
       </c>
     </row>
     <row r="11">
@@ -4652,10 +4804,10 @@
         <v>15.03486586444025</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>27.02548577965456</v>
+        <v>27.80094550302556</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>885.3090393449792</v>
+        <v>893.0685092378428</v>
       </c>
     </row>
     <row r="12">
@@ -4716,10 +4868,10 @@
         <v>9.426283186062674</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>14.49555841362105</v>
+        <v>15.22315692145569</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>282.2480999119129</v>
+        <v>285.6149967574684</v>
       </c>
     </row>
     <row r="13">
@@ -4780,10 +4932,10 @@
         <v>33.0329514654475</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>58.0347567603996</v>
+        <v>58.87947146078957</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>1355.144862677546</v>
+        <v>1355.147410893017</v>
       </c>
     </row>
     <row r="14">
@@ -4844,10 +4996,10 @@
         <v>12.0676187388962</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>20.49906051872934</v>
+        <v>20.99091903696784</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>432.8436615751133</v>
+        <v>434.8281344192733</v>
       </c>
     </row>
     <row r="15">
@@ -4908,10 +5060,10 @@
         <v>19.08757625289542</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>46.7474721700487</v>
+        <v>47.31961385542417</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>9484.22168125415</v>
+        <v>9575.82793905447</v>
       </c>
     </row>
     <row r="16">
@@ -4972,10 +5124,10 @@
         <v>14.62001358359223</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>27.27501890673397</v>
+        <v>27.228647470399</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>1088.130899207159</v>
+        <v>1101.749495821443</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5188,10 @@
         <v>10.58575795851373</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>20.36975065541514</v>
+        <v>20.64428368535122</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>516.4290962884709</v>
+        <v>528.2657917755482</v>
       </c>
     </row>
     <row r="18">
@@ -5100,10 +5252,10 @@
         <v>25.10851547873661</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>55.22309874951942</v>
+        <v>56.50856615727501</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>2911.506872009966</v>
+        <v>2975.579002503166</v>
       </c>
     </row>
     <row r="19">
@@ -5164,10 +5316,10 @@
         <v>21.57612803317968</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>45.9960971835885</v>
+        <v>46.81070411697132</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>1651.297669388214</v>
+        <v>1672.455667457177</v>
       </c>
     </row>
     <row r="20">
@@ -5228,10 +5380,10 @@
         <v>18.68870087436543</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>37.77244644400978</v>
+        <v>39.1877166043769</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>1198.654546275306</v>
+        <v>1213.262135702095</v>
       </c>
     </row>
     <row r="21">
@@ -5292,10 +5444,10 @@
         <v>43.46229997380868</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>104.1759895227009</v>
+        <v>105.7239991474317</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>10324.11340578559</v>
+        <v>10434.20305397692</v>
       </c>
     </row>
     <row r="22">
@@ -5356,10 +5508,10 @@
         <v>43.53974042495049</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>102.6358994158803</v>
+        <v>106.3053138103495</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>2879.68673097295</v>
+        <v>2997.14360767445</v>
       </c>
     </row>
     <row r="23">
@@ -5420,10 +5572,10 @@
         <v>34.50669720801918</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>74.09169294735712</v>
+        <v>75.45303358094377</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>1641.982431996448</v>
+        <v>1713.880119851711</v>
       </c>
     </row>
     <row r="24">
@@ -5484,10 +5636,10 @@
         <v>37.91331403836209</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>88.89981403961839</v>
+        <v>93.50696031756911</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>17974.53640870317</v>
+        <v>18646.39777322325</v>
       </c>
     </row>
     <row r="25">
@@ -5548,10 +5700,10 @@
         <v>52.2205997764563</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>129.6980123072925</v>
+        <v>129.0872419291629</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>24004.15401817341</v>
+        <v>24969.56818591674</v>
       </c>
     </row>
     <row r="26">
@@ -5612,10 +5764,10 @@
         <v>20.71388555405333</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>50.3959115437482</v>
+        <v>50.43510478193937</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>12282.13023893807</v>
+        <v>12443.76272454635</v>
       </c>
     </row>
     <row r="27">
@@ -5676,10 +5828,10 @@
         <v>47.52725536297364</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>113.0153773697735</v>
+        <v>113.3779049847686</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>12154.32549573633</v>
+        <v>12105.01830009212</v>
       </c>
     </row>
     <row r="28">
@@ -5740,10 +5892,10 @@
         <v>22.75842487225986</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>49.74485673692133</v>
+        <v>49.84638484300135</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>3344.866242802525</v>
+        <v>3474.675819710544</v>
       </c>
     </row>
     <row r="29">
@@ -5804,10 +5956,10 @@
         <v>9.928677610949343</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>19.67183116525803</v>
+        <v>19.88358891175121</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>1202.352845225761</v>
+        <v>1235.144456825275</v>
       </c>
     </row>
     <row r="30">
@@ -5868,10 +6020,10 @@
         <v>2.411197049506199</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>4.398871245422497</v>
+        <v>4.428691334695167</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>119.0056638813868</v>
+        <v>122.7578591745158</v>
       </c>
     </row>
     <row r="31">
@@ -5932,10 +6084,10 @@
         <v>3.427240296296283</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>5.34258783129383</v>
+        <v>5.382227747919267</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>90.27678652929225</v>
+        <v>92.56142322035174</v>
       </c>
     </row>
     <row r="32">
@@ -5996,10 +6148,10 @@
         <v>14.51519999999999</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>23.01940266069422</v>
+        <v>23.41279960152927</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>525.8903144616501</v>
+        <v>535.9284460891949</v>
       </c>
     </row>
     <row r="33">
@@ -6060,10 +6212,10 @@
         <v>1.016050000000002</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>1.609919456245935</v>
+        <v>1.626148015190646</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>61.77707253150518</v>
+        <v>63.78704641385172</v>
       </c>
     </row>
     <row r="34">
@@ -6124,10 +6276,10 @@
         <v>1.846527218407039</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>2.766602527455714</v>
+        <v>2.824619140814992</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>74.64268434486924</v>
+        <v>77.46539844155171</v>
       </c>
     </row>
     <row r="35">
@@ -6188,10 +6340,10 @@
         <v>5.78075187877349</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>10.92072730731952</v>
+        <v>11.03623657280822</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>813.6990521464184</v>
+        <v>791.2975748411623</v>
       </c>
     </row>
     <row r="36">
@@ -6316,10 +6468,10 @@
         <v>13.84143761892315</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>25.18266528060488</v>
+        <v>25.18512698027565</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>513.6177021092668</v>
+        <v>532.7860512352547</v>
       </c>
     </row>
     <row r="38">
@@ -6380,10 +6532,10 @@
         <v>3.36</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>4.232831923394609</v>
+        <v>4.311623214776216</v>
       </c>
       <c r="V38" s="2" t="n">
-        <v>80.80469344348158</v>
+        <v>82.2607328123313</v>
       </c>
     </row>
     <row r="39">
@@ -6792,7 +6944,7 @@
         <v>1.033687883819143</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.033758646737751</v>
+        <v>1.034702703725304</v>
       </c>
       <c r="V3" s="2" t="n">
         <v>0.9810424917673825</v>
@@ -6862,10 +7014,10 @@
         <v>375.5013578329761</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>945.9994391129031</v>
+        <v>964.2293310407301</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>162627.8755460127</v>
+        <v>171169.8746666788</v>
       </c>
     </row>
     <row r="5">
@@ -6932,10 +7084,10 @@
         <v>1748.991525587409</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>4234.200955594343</v>
+        <v>4302.54693696152</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>2783699.637979443</v>
+        <v>2858734.731157274</v>
       </c>
     </row>
     <row r="6">
@@ -7002,10 +7154,10 @@
         <v>6299.897452842601</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>15730.11281185321</v>
+        <v>16089.10938876302</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>734005.0939373279</v>
+        <v>754975.0603875497</v>
       </c>
     </row>
     <row r="7">
@@ -7072,10 +7224,10 @@
         <v>11273.11992558222</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>25666.09948170339</v>
+        <v>26556.26504751664</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>151110634.0087433</v>
+        <v>152627302.111988</v>
       </c>
     </row>
     <row r="8">
@@ -7142,10 +7294,10 @@
         <v>87.49926516181401</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>211.7252875596923</v>
+        <v>214.9287252815892</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>180288.1351579394</v>
+        <v>183923.261916347</v>
       </c>
     </row>
     <row r="9">
@@ -7212,10 +7364,10 @@
         <v>52.15574107332536</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>123.777048025753</v>
+        <v>124.5063141526616</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>20020.19981453731</v>
+        <v>20404.47103668627</v>
       </c>
     </row>
     <row r="10">
@@ -7282,10 +7434,10 @@
         <v>52.56298156164731</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>99.58627797081959</v>
+        <v>105.8607595152677</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>8678.285531710808</v>
+        <v>9021.195495274076</v>
       </c>
     </row>
     <row r="11">
@@ -7352,10 +7504,10 @@
         <v>22.90007446335974</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>41.26875900615609</v>
+        <v>42.39456486343174</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>1264.983099647077</v>
+        <v>1275.963462996302</v>
       </c>
     </row>
     <row r="12">
@@ -7422,10 +7574,10 @@
         <v>13.51008842270341</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>20.89090849916469</v>
+        <v>21.93998096833876</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>401.00975178813</v>
+        <v>405.7840844709587</v>
       </c>
     </row>
     <row r="13">
@@ -7492,10 +7644,10 @@
         <v>49.60035704610016</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>87.43592622102615</v>
+        <v>88.60729752359039</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>1933.297449097238</v>
+        <v>1933.149653098989</v>
       </c>
     </row>
     <row r="14">
@@ -7562,10 +7714,10 @@
         <v>18.28379112819732</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>31.39590496023486</v>
+        <v>32.08943304830522</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>619.2869036157231</v>
+        <v>622.0654430531074</v>
       </c>
     </row>
     <row r="15">
@@ -7632,10 +7784,10 @@
         <v>41.2346051031607</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>97.03539565017701</v>
+        <v>97.69988814269161</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>13861.14466607727</v>
+        <v>13990.40533945842</v>
       </c>
     </row>
     <row r="16">
@@ -7702,10 +7854,10 @@
         <v>27.69226506314409</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>51.08652538924518</v>
+        <v>50.79690729593496</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>1583.055335082336</v>
+        <v>1602.140499612354</v>
       </c>
     </row>
     <row r="17">
@@ -7772,10 +7924,10 @@
         <v>21.62203433783599</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>40.80016889209886</v>
+        <v>41.10994288576095</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>755.9323966808696</v>
+        <v>772.8955493412088</v>
       </c>
     </row>
     <row r="18">
@@ -7842,10 +7994,10 @@
         <v>44.28279129788718</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>96.49456032822332</v>
+        <v>98.33181592172483</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>4223.423587027402</v>
+        <v>4315.276633604712</v>
       </c>
     </row>
     <row r="19">
@@ -7912,10 +8064,10 @@
         <v>43.27990283610434</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>90.16623367043573</v>
+        <v>91.24424267647014</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>2398.312330243016</v>
+        <v>2428.836762865972</v>
       </c>
     </row>
     <row r="20">
@@ -7982,10 +8134,10 @@
         <v>34.55495975625556</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>69.27887552808545</v>
+        <v>71.46277863009229</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>1737.953877813758</v>
+        <v>1758.686511539419</v>
       </c>
     </row>
     <row r="21">
@@ -8052,10 +8204,10 @@
         <v>90.70820640171084</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>211.0897575061378</v>
+        <v>213.0768984955218</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>15077.93909014276</v>
+        <v>15231.97284803453</v>
       </c>
     </row>
     <row r="22">
@@ -8122,10 +8274,10 @@
         <v>91.38801118266895</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>210.1907119127182</v>
+        <v>216.473301797715</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>4223.501887100795</v>
+        <v>4393.486978686482</v>
       </c>
     </row>
     <row r="23">
@@ -8192,10 +8344,10 @@
         <v>50.97476634219117</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>109.1509632691433</v>
+        <v>111.1558474145388</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>2336.777510233704</v>
+        <v>2438.947746756535</v>
       </c>
     </row>
     <row r="24">
@@ -8262,10 +8414,10 @@
         <v>65.35182978189683</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>154.768452182884</v>
+        <v>161.744541181149</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>26091.27428946537</v>
+        <v>27059.64822683251</v>
       </c>
     </row>
     <row r="25">
@@ -8332,10 +8484,10 @@
         <v>97.0493206279677</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>239.4241937511616</v>
+        <v>236.9555503827281</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>34896.17078428387</v>
+        <v>36288.2726685448</v>
       </c>
     </row>
     <row r="26">
@@ -8402,10 +8554,10 @@
         <v>38.1595557303455</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>93.26120341752659</v>
+        <v>92.54017004164719</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>17891.41918216844</v>
+        <v>18119.63361450618</v>
       </c>
     </row>
     <row r="27">
@@ -8472,10 +8624,10 @@
         <v>96.94548683008421</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>227.1783906847331</v>
+        <v>226.2014925273851</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>17769.4668081431</v>
+        <v>17690.62826767249</v>
       </c>
     </row>
     <row r="28">
@@ -8542,10 +8694,10 @@
         <v>52.82886486732836</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>110.3136478741529</v>
+        <v>109.6112088765447</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>4926.067704415977</v>
+        <v>5115.038689195876</v>
       </c>
     </row>
     <row r="29">
@@ -8612,10 +8764,10 @@
         <v>16.1840750155305</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>32.04564613386857</v>
+        <v>32.28677186035279</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>1728.283473374919</v>
+        <v>1775.112324617013</v>
       </c>
     </row>
     <row r="30">
@@ -8682,10 +8834,10 @@
         <v>8.00436988474663</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>13.60413694183073</v>
+        <v>13.539814044916</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>179.5019280626416</v>
+        <v>184.933078657571</v>
       </c>
     </row>
     <row r="31">
@@ -8752,10 +8904,10 @@
         <v>8.448598129593863</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>12.70653178271755</v>
+        <v>12.68070673687564</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>133.2879533171306</v>
+        <v>136.520004315677</v>
       </c>
     </row>
     <row r="32">
@@ -8822,10 +8974,10 @@
         <v>23.92258669306121</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>36.96717003729928</v>
+        <v>37.54761949886471</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>751.2499496920868</v>
+        <v>765.5198801150671</v>
       </c>
     </row>
     <row r="33">
@@ -8892,10 +9044,10 @@
         <v>3.058348349766994</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>4.550134030463092</v>
+        <v>4.556293668393119</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>93.56539300393216</v>
+        <v>96.44722636844091</v>
       </c>
     </row>
     <row r="34">
@@ -8962,10 +9114,10 @@
         <v>5.693764039826799</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>8.190246146247651</v>
+        <v>8.298344895730454</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>114.8464853525946</v>
+        <v>118.9310592810974</v>
       </c>
     </row>
     <row r="35">
@@ -9032,10 +9184,10 @@
         <v>9.498851850453693</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>17.77653394084422</v>
+        <v>17.93270706228341</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>1167.450595949021</v>
+        <v>1135.088390380274</v>
       </c>
     </row>
     <row r="36">
@@ -9102,10 +9254,10 @@
         <v>2.756501023517723</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>3.493545682743196</v>
+        <v>3.417353945442033</v>
       </c>
       <c r="V36" s="2" t="n">
-        <v>3.491614479683113</v>
+        <v>3.409847954707133</v>
       </c>
     </row>
     <row r="37">
@@ -9172,10 +9324,10 @@
         <v>19.97097312655629</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>36.35480887328039</v>
+        <v>36.36836867808593</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>729.6263333958011</v>
+        <v>756.8536318254826</v>
       </c>
     </row>
     <row r="38">
@@ -9242,10 +9394,10 @@
         <v>4.848510552699566</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>6.108996628221276</v>
+        <v>6.224783202933654</v>
       </c>
       <c r="V38" s="2" t="n">
-        <v>114.7787667873213</v>
+        <v>116.84699322354</v>
       </c>
     </row>
     <row r="39">
@@ -9666,7 +9818,7 @@
         <v>1.033687883819143</v>
       </c>
       <c r="U3" s="2" t="n">
-        <v>1.033758646737751</v>
+        <v>1.034702703725304</v>
       </c>
       <c r="V3" s="2" t="n">
         <v>0.9810424917673825</v>
@@ -9736,10 +9888,10 @@
         <v>375.5013578329761</v>
       </c>
       <c r="U4" s="2" t="n">
-        <v>945.9994391129031</v>
+        <v>964.2293310407301</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>162627.8755460127</v>
+        <v>171169.8746666788</v>
       </c>
     </row>
     <row r="5">
@@ -9806,10 +9958,10 @@
         <v>1748.991525587409</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>4234.200955594343</v>
+        <v>4302.54693696152</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>2783699.637979443</v>
+        <v>2858734.731157274</v>
       </c>
     </row>
     <row r="6">
@@ -9876,10 +10028,10 @@
         <v>6299.897452842601</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>15730.11281185321</v>
+        <v>16089.10938876302</v>
       </c>
       <c r="V6" s="2" t="n">
-        <v>734005.0939373279</v>
+        <v>754975.0603875497</v>
       </c>
     </row>
     <row r="7">
@@ -9946,10 +10098,10 @@
         <v>11273.11992558222</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>25666.09948170339</v>
+        <v>26556.26504751664</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>151110634.0087433</v>
+        <v>152627302.111988</v>
       </c>
     </row>
     <row r="8">
@@ -10016,10 +10168,10 @@
         <v>87.49926516181401</v>
       </c>
       <c r="U8" s="2" t="n">
-        <v>211.7252875596923</v>
+        <v>214.9287252815892</v>
       </c>
       <c r="V8" s="2" t="n">
-        <v>180288.1351579394</v>
+        <v>183923.261916347</v>
       </c>
     </row>
     <row r="9">
@@ -10086,10 +10238,10 @@
         <v>52.15574107332536</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>123.777048025753</v>
+        <v>124.5063141526616</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>20020.19981453731</v>
+        <v>20404.47103668627</v>
       </c>
     </row>
     <row r="10">
@@ -10156,10 +10308,10 @@
         <v>52.56298156164731</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>99.58627797081959</v>
+        <v>105.8607595152677</v>
       </c>
       <c r="V10" s="2" t="n">
-        <v>8678.285531710808</v>
+        <v>9021.195495274076</v>
       </c>
     </row>
     <row r="11">
@@ -10226,10 +10378,10 @@
         <v>22.90007446335974</v>
       </c>
       <c r="U11" s="2" t="n">
-        <v>41.26875900615609</v>
+        <v>42.39456486343174</v>
       </c>
       <c r="V11" s="2" t="n">
-        <v>1264.983099647077</v>
+        <v>1275.963462996302</v>
       </c>
     </row>
     <row r="12">
@@ -10296,10 +10448,10 @@
         <v>13.51008842270341</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>20.89090849916469</v>
+        <v>21.93998096833876</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>401.00975178813</v>
+        <v>405.7840844709587</v>
       </c>
     </row>
     <row r="13">
@@ -10366,10 +10518,10 @@
         <v>49.60035704610016</v>
       </c>
       <c r="U13" s="2" t="n">
-        <v>87.43592622102615</v>
+        <v>88.60729752359039</v>
       </c>
       <c r="V13" s="2" t="n">
-        <v>1933.297449097238</v>
+        <v>1933.149653098989</v>
       </c>
     </row>
     <row r="14">
@@ -10436,10 +10588,10 @@
         <v>18.28379112819732</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>31.39590496023486</v>
+        <v>32.08943304830522</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>619.2869036157231</v>
+        <v>622.0654430531074</v>
       </c>
     </row>
     <row r="15">
@@ -10506,10 +10658,10 @@
         <v>41.2346051031607</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>97.03539565017701</v>
+        <v>97.69988814269161</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>13861.14466607727</v>
+        <v>13990.40533945842</v>
       </c>
     </row>
     <row r="16">
@@ -10576,10 +10728,10 @@
         <v>27.69226506314409</v>
       </c>
       <c r="U16" s="2" t="n">
-        <v>51.08652538924518</v>
+        <v>50.79690729593496</v>
       </c>
       <c r="V16" s="2" t="n">
-        <v>1583.055335082336</v>
+        <v>1602.140499612354</v>
       </c>
     </row>
     <row r="17">
@@ -10646,10 +10798,10 @@
         <v>21.62203433783599</v>
       </c>
       <c r="U17" s="2" t="n">
-        <v>40.80016889209886</v>
+        <v>41.10994288576095</v>
       </c>
       <c r="V17" s="2" t="n">
-        <v>755.9323966808696</v>
+        <v>772.8955493412088</v>
       </c>
     </row>
     <row r="18">
@@ -10716,10 +10868,10 @@
         <v>44.28279129788718</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>96.49456032822332</v>
+        <v>98.33181592172483</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>4223.423587027402</v>
+        <v>4315.276633604712</v>
       </c>
     </row>
     <row r="19">
@@ -10786,10 +10938,10 @@
         <v>43.27990283610434</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>90.16623367043573</v>
+        <v>91.24424267647014</v>
       </c>
       <c r="V19" s="2" t="n">
-        <v>2398.312330243016</v>
+        <v>2428.836762865972</v>
       </c>
     </row>
     <row r="20">
@@ -10856,10 +11008,10 @@
         <v>34.55495975625556</v>
       </c>
       <c r="U20" s="2" t="n">
-        <v>69.27887552808545</v>
+        <v>71.46277863009229</v>
       </c>
       <c r="V20" s="2" t="n">
-        <v>1737.953877813758</v>
+        <v>1758.686511539419</v>
       </c>
     </row>
     <row r="21">
@@ -10926,10 +11078,10 @@
         <v>90.70820640171084</v>
       </c>
       <c r="U21" s="2" t="n">
-        <v>211.0897575061378</v>
+        <v>213.0768984955218</v>
       </c>
       <c r="V21" s="2" t="n">
-        <v>15077.93909014276</v>
+        <v>15231.97284803453</v>
       </c>
     </row>
     <row r="22">
@@ -10996,10 +11148,10 @@
         <v>91.38801118266895</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>210.1907119127182</v>
+        <v>216.473301797715</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>4223.501887100795</v>
+        <v>4393.486978686482</v>
       </c>
     </row>
     <row r="23">
@@ -11066,10 +11218,10 @@
         <v>50.97476634219117</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>109.1509632691433</v>
+        <v>111.1558474145388</v>
       </c>
       <c r="V23" s="2" t="n">
-        <v>2336.777510233704</v>
+        <v>2438.947746756535</v>
       </c>
     </row>
     <row r="24">
@@ -11136,10 +11288,10 @@
         <v>65.35182978189683</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>154.768452182884</v>
+        <v>161.744541181149</v>
       </c>
       <c r="V24" s="2" t="n">
-        <v>26091.27428946537</v>
+        <v>27059.64822683251</v>
       </c>
     </row>
     <row r="25">
@@ -11206,10 +11358,10 @@
         <v>97.0493206279677</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>239.4241937511616</v>
+        <v>236.9555503827281</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>34896.17078428387</v>
+        <v>36288.2726685448</v>
       </c>
     </row>
     <row r="26">
@@ -11276,10 +11428,10 @@
         <v>38.1595557303455</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>93.26120341752659</v>
+        <v>92.54017004164719</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>17891.41918216844</v>
+        <v>18119.63361450618</v>
       </c>
     </row>
     <row r="27">
@@ -11346,10 +11498,10 @@
         <v>96.94548683008421</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>227.1783906847331</v>
+        <v>226.2014925273851</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>17769.4668081431</v>
+        <v>17690.62826767249</v>
       </c>
     </row>
     <row r="28">
@@ -11416,10 +11568,10 @@
         <v>52.82886486732836</v>
       </c>
       <c r="U28" s="2" t="n">
-        <v>110.3136478741529</v>
+        <v>109.6112088765447</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>4926.067704415977</v>
+        <v>5115.038689195876</v>
       </c>
     </row>
     <row r="29">
@@ -11486,10 +11638,10 @@
         <v>16.1840750155305</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>32.04564613386857</v>
+        <v>32.28677186035279</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>1728.283473374919</v>
+        <v>1775.112324617013</v>
       </c>
     </row>
     <row r="30">
@@ -11556,10 +11708,10 @@
         <v>8.00436988474663</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>13.60413694183073</v>
+        <v>13.539814044916</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>179.5019280626416</v>
+        <v>184.933078657571</v>
       </c>
     </row>
     <row r="31">
@@ -11626,10 +11778,10 @@
         <v>8.448598129593863</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>12.70653178271755</v>
+        <v>12.68070673687564</v>
       </c>
       <c r="V31" s="2" t="n">
-        <v>133.2879533171306</v>
+        <v>136.520004315677</v>
       </c>
     </row>
     <row r="32">
@@ -11696,10 +11848,10 @@
         <v>23.92258669306121</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>36.96717003729928</v>
+        <v>37.54761949886471</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>751.2499496920868</v>
+        <v>765.5198801150671</v>
       </c>
     </row>
     <row r="33">
@@ -11766,10 +11918,10 @@
         <v>3.058348349766994</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>4.550134030463092</v>
+        <v>4.556293668393119</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>93.56539300393216</v>
+        <v>96.44722636844091</v>
       </c>
     </row>
     <row r="34">
@@ -11836,10 +11988,10 @@
         <v>5.693764039826799</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>8.190246146247651</v>
+        <v>8.298344895730454</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>114.8464853525946</v>
+        <v>118.9310592810974</v>
       </c>
     </row>
     <row r="35">
@@ -11906,10 +12058,10 @@
         <v>9.498851850453693</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>17.77653394084422</v>
+        <v>17.93270706228341</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>1167.450595949021</v>
+        <v>1135.088390380274</v>
       </c>
     </row>
     <row r="36">
@@ -11976,10 +12128,10 @@
         <v>2.756501023517723</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>3.493545682743196</v>
+        <v>3.417353945442033</v>
       </c>
       <c r="V36" s="2" t="n">
-        <v>3.491614479683113</v>
+        <v>3.409847954707133</v>
       </c>
     </row>
     <row r="37">
@@ -12046,10 +12198,10 @@
         <v>19.97097312655629</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>36.35480887328039</v>
+        <v>36.36836867808593</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>729.6263333958011</v>
+        <v>756.8536318254826</v>
       </c>
     </row>
     <row r="38">
@@ -12116,10 +12268,10 @@
         <v>4.848510552699566</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>6.108996628221276</v>
+        <v>6.224783202933654</v>
       </c>
       <c r="V38" s="2" t="n">
-        <v>114.7787667873213</v>
+        <v>116.84699322354</v>
       </c>
     </row>
     <row r="39">
@@ -13711,22 +13863,22 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>65.86630273973515</v>
+        <v>66.65604438220892</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>65.86630273973515</v>
+        <v>66.65604438220892</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>35.38290271054822</v>
+        <v>36.06214283385852</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>130696.17</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>0.0005039650568163945</v>
+        <v>0.0005100076335994308</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.0002707263932106673</v>
+        <v>0.0002759234860046665</v>
       </c>
     </row>
     <row r="21">
@@ -13736,22 +13888,22 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>7061.32739619984</v>
+        <v>7181.960426413685</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>7061.32739619984</v>
+        <v>7181.960426413685</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>4856.191595410607</v>
+        <v>4940.872185049964</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>130696.17</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>0.05402857173396772</v>
+        <v>0.05495157529416268</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.03715634203672998</v>
+        <v>0.03780426147950598</v>
       </c>
     </row>
   </sheetData>
@@ -13827,10 +13979,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -13855,10 +14007,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -14054,7 +14206,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Christensen &amp; Pauly (1995): per-group TE^(1-TL) with global_TE=0.1.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE=0.1.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -14071,7 +14223,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Christensen &amp; Pauly (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">

--- a/PPREstimation/output/top10/36_2_South_China_Sea_SCS-2007_Northern_South_China_Sea_(1970s).xlsx
+++ b/PPREstimation/output/top10/36_2_South_China_Sea_SCS-2007_Northern_South_China_Sea_(1970s).xlsx
@@ -617,7 +617,6 @@
           <t>Import</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>1</v>
       </c>
@@ -640,10 +639,10 @@
         <v>0</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>0</v>
@@ -4037,7 +4036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:X40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4175,6 +4174,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -4185,9 +4194,6 @@
           <t>diet_import</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
@@ -4218,19 +4224,19 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4243,9 +4249,6 @@
           <t>Detritus</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="2" t="n">
         <v>0</v>
       </c>
@@ -4295,6 +4298,9 @@
         <v>0</v>
       </c>
       <c r="V3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4307,11 +4313,8 @@
           <t>Marine turtles</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="2" t="n">
-        <v>327.1769560252093</v>
+        <v>306589312.0197726</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>64431.79973935651</v>
@@ -4360,6 +4363,9 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>117845.4613958489</v>
+      </c>
+      <c r="X4" t="n">
+        <v>318.8506706250615</v>
       </c>
     </row>
     <row r="5">
@@ -4371,11 +4377,8 @@
           <t>Other mammals</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="2" t="n">
-        <v>504.3550821607488</v>
+        <v>157988472.1211756</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>1289709.957861404</v>
@@ -4424,6 +4427,9 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>1977457.18367944</v>
+      </c>
+      <c r="X5" t="n">
+        <v>493.1090446512209</v>
       </c>
     </row>
     <row r="6">
@@ -4435,11 +4441,8 @@
           <t>Pinnipeds</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="2" t="n">
-        <v>612.0327132589003</v>
+        <v>101374151.8159148</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>362396.0213868935</v>
@@ -4488,6 +4491,9 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>520820.5319576079</v>
+      </c>
+      <c r="X6" t="n">
+        <v>597.690508201643</v>
       </c>
     </row>
     <row r="7">
@@ -4499,11 +4505,8 @@
           <t>Seabirds</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="2" t="n">
-        <v>293.15844512519</v>
+        <v>14927114.50573042</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>79240872.80987757</v>
@@ -4552,6 +4555,9 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>105868755.5056871</v>
+      </c>
+      <c r="X7" t="n">
+        <v>286.5963961135019</v>
       </c>
     </row>
     <row r="8">
@@ -4563,11 +4569,8 @@
           <t>Pelagic sharks and rays</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="2" t="n">
-        <v>477.2934070236491</v>
+        <v>28044039.75219103</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>86321.8340127571</v>
@@ -4616,6 +4619,9 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>127625.7634441447</v>
+      </c>
+      <c r="X8" t="n">
+        <v>467.2533996521511</v>
       </c>
     </row>
     <row r="9">
@@ -4627,11 +4633,8 @@
           <t>Demersal sharks and rays</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="2" t="n">
-        <v>265.2965728846619</v>
+        <v>113391773.7758719</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>7268.387336421263</v>
@@ -4680,6 +4683,9 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>13974.15801482531</v>
+      </c>
+      <c r="X9" t="n">
+        <v>258.9144218754794</v>
       </c>
     </row>
     <row r="10">
@@ -4691,11 +4697,8 @@
           <t>Pelagic fish (&gt; 30 cm)</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="2" t="n">
-        <v>153.0947547525519</v>
+        <v>18571881.43090333</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>5230.458762696133</v>
@@ -4744,6 +4747,9 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>6298.948576694078</v>
+      </c>
+      <c r="X10" t="n">
+        <v>150.3852387976852</v>
       </c>
     </row>
     <row r="11">
@@ -4755,11 +4761,8 @@
           <t>Juvenile large pelagic fish</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" s="2" t="n">
-        <v>63.0731683274706</v>
+        <v>266100.5800094504</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>824.3971345479144</v>
@@ -4808,6 +4811,9 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>893.0685092378428</v>
+      </c>
+      <c r="X11" t="n">
+        <v>62.0757057803901</v>
       </c>
     </row>
     <row r="12">
@@ -4819,11 +4825,8 @@
           <t>Pelagic fish (≤ 30 cm)</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" s="2" t="n">
-        <v>31.53893627705428</v>
+        <v>1993.394013147378</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>277.0688012490693</v>
@@ -4872,6 +4875,9 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>285.6149967574684</v>
+      </c>
+      <c r="X12" t="n">
+        <v>31.19308455081351</v>
       </c>
     </row>
     <row r="13">
@@ -4883,11 +4889,8 @@
           <t>Melon seed</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" s="2" t="n">
-        <v>60.31973955725809</v>
+        <v>315505.3808614618</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>1177.161539645402</v>
@@ -4936,6 +4939,9 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>1355.147410893017</v>
+      </c>
+      <c r="X13" t="n">
+        <v>59.38778319164236</v>
       </c>
     </row>
     <row r="14">
@@ -4947,11 +4953,8 @@
           <t>Benthopelagic fish</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" s="2" t="n">
-        <v>45.34486377557898</v>
+        <v>32593.39970551777</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>356.106350152858</v>
@@ -5000,6 +5003,9 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>434.8281344192733</v>
+      </c>
+      <c r="X14" t="n">
+        <v>44.70814354100692</v>
       </c>
     </row>
     <row r="15">
@@ -5011,11 +5017,8 @@
           <t>Adult demersal fish (&gt; 30 cm)</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" s="2" t="n">
-        <v>206.1377458959708</v>
+        <v>83003421.3635617</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>5355.565531893129</v>
@@ -5064,6 +5067,9 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>9575.82793905447</v>
+      </c>
+      <c r="X15" t="n">
+        <v>201.256827972596</v>
       </c>
     </row>
     <row r="16">
@@ -5075,11 +5081,8 @@
           <t>Juvenile demersal fish (&gt; 30 cm)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="2" t="n">
-        <v>54.87236204540365</v>
+        <v>598850.3504563477</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>929.511216977587</v>
@@ -5128,6 +5131,9 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>1101.749495821443</v>
+      </c>
+      <c r="X16" t="n">
+        <v>53.96904598541789</v>
       </c>
     </row>
     <row r="17">
@@ -5139,11 +5145,8 @@
           <t>Demesral fish (≤ 30 cm)</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" s="2" t="n">
-        <v>47.82143364959593</v>
+        <v>284212.5206831223</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>386.2984287983117</v>
@@ -5192,6 +5195,9 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>528.2657917755482</v>
+      </c>
+      <c r="X17" t="n">
+        <v>47.01684212908239</v>
       </c>
     </row>
     <row r="18">
@@ -5203,11 +5209,8 @@
           <t>Croakers (&gt; 30 cm)</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" s="2" t="n">
-        <v>204.005073035124</v>
+        <v>14291058.56786717</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>2210.925841951306</v>
@@ -5256,6 +5259,9 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>2975.579002503166</v>
+      </c>
+      <c r="X18" t="n">
+        <v>199.8328285315637</v>
       </c>
     </row>
     <row r="19">
@@ -5267,11 +5273,8 @@
           <t>Juvenile large croakers</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" s="2" t="n">
-        <v>115.0106060527395</v>
+        <v>5823701.275662489</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>1215.55248002888</v>
@@ -5320,6 +5323,9 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>1672.455667457177</v>
+      </c>
+      <c r="X19" t="n">
+        <v>112.6334560188329</v>
       </c>
     </row>
     <row r="20">
@@ -5331,11 +5337,8 @@
           <t>Croakers (≤ 30 cm)</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" s="2" t="n">
-        <v>119.6836884612146</v>
+        <v>1765893.991615217</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>960.5105986344158</v>
@@ -5384,6 +5387,9 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>1213.262135702095</v>
+      </c>
+      <c r="X20" t="n">
+        <v>117.4282714397407</v>
       </c>
     </row>
     <row r="21">
@@ -5395,11 +5401,8 @@
           <t>Adult groupers</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" s="2" t="n">
-        <v>289.3360043196629</v>
+        <v>52027107.26708748</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>7059.021807312628</v>
@@ -5448,6 +5451,9 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>10434.20305397692</v>
+      </c>
+      <c r="X21" t="n">
+        <v>282.8481893298627</v>
       </c>
     </row>
     <row r="22">
@@ -5459,11 +5465,8 @@
           <t>Snappers</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" s="2" t="n">
-        <v>267.0527307971647</v>
+        <v>11759220.47120559</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>2184.150637579365</v>
@@ -5512,6 +5515,9 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>2997.14360767445</v>
+      </c>
+      <c r="X22" t="n">
+        <v>261.151531956041</v>
       </c>
     </row>
     <row r="23">
@@ -5523,11 +5529,8 @@
           <t>Pomfret (stromateids)</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" s="2" t="n">
-        <v>174.4339134757371</v>
+        <v>163767.8019059463</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1107.715093820353</v>
@@ -5576,6 +5579,9 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>1713.880119851711</v>
+      </c>
+      <c r="X23" t="n">
+        <v>171.4873874154518</v>
       </c>
     </row>
     <row r="24">
@@ -5587,11 +5593,8 @@
           <t>Adult hairtail (trichiurids)</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" s="2" t="n">
-        <v>461.9722189011516</v>
+        <v>135105564.1970818</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>9951.351132579408</v>
@@ -5640,6 +5643,9 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>18646.39777322325</v>
+      </c>
+      <c r="X24" t="n">
+        <v>451.4584999402386</v>
       </c>
     </row>
     <row r="25">
@@ -5651,11 +5657,8 @@
           <t>Juvenile Hairtail (trichiurids)</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" s="2" t="n">
-        <v>471.7762019020884</v>
+        <v>91116661.22312379</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>12847.45959582737</v>
@@ -5704,6 +5707,9 @@
       </c>
       <c r="V25" s="2" t="n">
         <v>24969.56818591674</v>
+      </c>
+      <c r="X25" t="n">
+        <v>460.7497645091067</v>
       </c>
     </row>
     <row r="26">
@@ -5715,11 +5721,8 @@
           <t>Lizard fish (synodontids)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" s="2" t="n">
-        <v>334.2253689067176</v>
+        <v>36215476.90322966</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>6549.676201336678</v>
@@ -5768,6 +5771,9 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>12443.76272454635</v>
+      </c>
+      <c r="X26" t="n">
+        <v>326.9858757069476</v>
       </c>
     </row>
     <row r="27">
@@ -5779,11 +5785,8 @@
           <t>Bigeyes (priacanthids)</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" s="2" t="n">
-        <v>193.8134635685486</v>
+        <v>12199287.64160669</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>7254.269109366923</v>
@@ -5832,6 +5835,9 @@
       </c>
       <c r="V27" s="2" t="n">
         <v>12105.01830009212</v>
+      </c>
+      <c r="X27" t="n">
+        <v>189.5324497079853</v>
       </c>
     </row>
     <row r="28">
@@ -5843,11 +5849,8 @@
           <t>Threadfin bream (nemipterids)</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" s="2" t="n">
-        <v>75.29344005280217</v>
+        <v>1680573.295470727</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>2351.601599047173</v>
@@ -5896,6 +5899,9 @@
       </c>
       <c r="V28" s="2" t="n">
         <v>3474.675819710544</v>
+      </c>
+      <c r="X28" t="n">
+        <v>73.81315725614151</v>
       </c>
     </row>
     <row r="29">
@@ -5907,11 +5913,8 @@
           <t>Cephalopods</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" s="2" t="n">
-        <v>99.09704477108096</v>
+        <v>252175.3792577987</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>726.7682741138451</v>
@@ -5960,6 +5963,9 @@
       </c>
       <c r="V29" s="2" t="n">
         <v>1235.144456825275</v>
+      </c>
+      <c r="X29" t="n">
+        <v>97.38497280476474</v>
       </c>
     </row>
     <row r="30">
@@ -5971,11 +5977,8 @@
           <t>Crabs</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" s="2" t="n">
-        <v>15.00784711288994</v>
+        <v>18724.86070605622</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>98.7200915839902</v>
@@ -6024,6 +6027,9 @@
       </c>
       <c r="V30" s="2" t="n">
         <v>122.7578591745158</v>
+      </c>
+      <c r="X30" t="n">
+        <v>14.76721796252587</v>
       </c>
     </row>
     <row r="31">
@@ -6035,11 +6041,8 @@
           <t>Shrimps</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" s="2" t="n">
-        <v>8.702251849840362</v>
+        <v>426.2164918374368</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>88.67433498275575</v>
@@ -6088,6 +6091,9 @@
       </c>
       <c r="V31" s="2" t="n">
         <v>92.56142322035174</v>
+      </c>
+      <c r="X31" t="n">
+        <v>8.611278178756708</v>
       </c>
     </row>
     <row r="32">
@@ -6099,11 +6105,8 @@
           <t>Sessile/other invertebrates</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" s="2" t="n">
-        <v>23.51765216041886</v>
+        <v>1298.748386605108</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>516.1583978152009</v>
@@ -6152,6 +6155,9 @@
       </c>
       <c r="V32" s="2" t="n">
         <v>535.9284460891949</v>
+      </c>
+      <c r="X32" t="n">
+        <v>23.25465911280694</v>
       </c>
     </row>
     <row r="33">
@@ -6163,11 +6169,8 @@
           <t>Non-ceph molluscs</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" s="2" t="n">
-        <v>5.373346462213778</v>
+        <v>842.7274005816791</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>57.39540349546976</v>
@@ -6216,6 +6219,9 @@
       </c>
       <c r="V33" s="2" t="n">
         <v>63.78704641385172</v>
+      </c>
+      <c r="X33" t="n">
+        <v>5.312720976788913</v>
       </c>
     </row>
     <row r="34">
@@ -6227,11 +6233,8 @@
           <t>Benthic crustaceans</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" s="2" t="n">
-        <v>7.006190450793072</v>
+        <v>3941.735230206961</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>71.47126293626472</v>
@@ -6280,6 +6283,9 @@
       </c>
       <c r="V34" s="2" t="n">
         <v>77.46539844155171</v>
+      </c>
+      <c r="X34" t="n">
+        <v>6.9179327020154</v>
       </c>
     </row>
     <row r="35">
@@ -6291,11 +6297,8 @@
           <t>Echinoderms</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" s="2" t="n">
-        <v>24.29266066048216</v>
+        <v>10541.43134830839</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>418.5939275816808</v>
@@ -6344,6 +6347,9 @@
       </c>
       <c r="V35" s="2" t="n">
         <v>791.2975748411623</v>
+      </c>
+      <c r="X35" t="n">
+        <v>23.93286803636964</v>
       </c>
     </row>
     <row r="36">
@@ -6355,9 +6361,6 @@
           <t>Polychaetes</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" s="2" t="n">
         <v>0</v>
       </c>
@@ -6407,6 +6410,9 @@
         <v>0</v>
       </c>
       <c r="V36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6419,11 +6425,8 @@
           <t>Jellyfish</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" s="2" t="n">
-        <v>39.76055438455198</v>
+        <v>4054.249871672462</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>328.2383785938518</v>
@@ -6472,6 +6475,9 @@
       </c>
       <c r="V37" s="2" t="n">
         <v>532.7860512352547</v>
+      </c>
+      <c r="X37" t="n">
+        <v>39.29202601221798</v>
       </c>
     </row>
     <row r="38">
@@ -6483,11 +6489,8 @@
           <t>Zooplankton</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" s="2" t="n">
-        <v>5.238058882240825</v>
+        <v>38.92565286593525</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>80.76923076923053</v>
@@ -6536,6 +6539,9 @@
       </c>
       <c r="V38" s="2" t="n">
         <v>82.2607328123313</v>
+      </c>
+      <c r="X38" t="n">
+        <v>5.208688475192973</v>
       </c>
     </row>
     <row r="39">
@@ -6547,9 +6553,6 @@
           <t>Benthic producer</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" s="2" t="n">
         <v>1</v>
       </c>
@@ -6601,6 +6604,9 @@
       <c r="V39" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="X39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -6611,9 +6617,6 @@
           <t>Phytoplankton</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" s="2" t="n">
         <v>1</v>
       </c>
@@ -6663,6 +6666,9 @@
         <v>1</v>
       </c>
       <c r="V40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6677,7 +6683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:X40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -6815,6 +6821,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -6864,19 +6880,22 @@
       <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6949,6 +6968,12 @@
       <c r="V3" s="2" t="n">
         <v>0.9810424917673825</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -6966,10 +6991,10 @@
         <v>92.36817646243769</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>52.24066894619853</v>
+        <v>2692.201195451597</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>644.4329212894243</v>
+        <v>529081636.8323154</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>94248.91488281998</v>
@@ -7018,6 +7043,12 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>171169.8746666788</v>
+      </c>
+      <c r="W4" t="n">
+        <v>51.66648764020988</v>
+      </c>
+      <c r="X4" t="n">
+        <v>627.7811065825483</v>
       </c>
     </row>
     <row r="5">
@@ -7036,10 +7067,10 @@
         <v>804.9195518555838</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>346.6074198764927</v>
+        <v>117743.9698590211</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>889.0690031283369</v>
+        <v>272480122.5285062</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>1874464.079650443</v>
@@ -7088,6 +7119,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>2858734.731157274</v>
+      </c>
+      <c r="W5" t="n">
+        <v>340.9903037368433</v>
+      </c>
+      <c r="X5" t="n">
+        <v>868.769579273888</v>
       </c>
     </row>
     <row r="6">
@@ -7106,10 +7143,10 @@
         <v>1309.957766003465</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>530.5280675169544</v>
+        <v>275450.6106944028</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1251.989192473138</v>
+        <v>174871731.5548666</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>529369.1988808451</v>
@@ -7158,6 +7195,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>754975.0603875497</v>
+      </c>
+      <c r="W6" t="n">
+        <v>521.3099884589022</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1222.744857278365</v>
       </c>
     </row>
     <row r="7">
@@ -7176,10 +7219,10 @@
         <v>252.7372954965662</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>125.9235032748216</v>
+        <v>15595.1383676661</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>559.5202679373864</v>
+        <v>25661835.79016795</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>114992570.5967543</v>
@@ -7228,6 +7271,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>152627302.111988</v>
+      </c>
+      <c r="W7" t="n">
+        <v>124.2337220943735</v>
+      </c>
+      <c r="X7" t="n">
+        <v>547.0691242980095</v>
       </c>
     </row>
     <row r="8">
@@ -7246,10 +7295,10 @@
         <v>908.9880051560747</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>385.4728863525418</v>
+        <v>145576.6960244619</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>784.4685456782904</v>
+        <v>48080410.42140355</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>125208.7929524061</v>
@@ -7298,6 +7347,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>183923.261916347</v>
+      </c>
+      <c r="W8" t="n">
+        <v>379.1133335324108</v>
+      </c>
+      <c r="X8" t="n">
+        <v>767.7179194002755</v>
       </c>
     </row>
     <row r="9">
@@ -7316,10 +7371,10 @@
         <v>308.6860101337908</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>149.9746627449809</v>
+        <v>22108.04252509096</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>602.3668038671244</v>
+        <v>195781560.0391699</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>10706.10148649219</v>
@@ -7368,6 +7423,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>20404.47103668627</v>
+      </c>
+      <c r="W9" t="n">
+        <v>147.8898989820327</v>
+      </c>
+      <c r="X9" t="n">
+        <v>588.1973200515148</v>
       </c>
     </row>
     <row r="10">
@@ -7386,10 +7447,10 @@
         <v>231.7551372376293</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>116.7365209876158</v>
+        <v>13406.0954074146</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>243.5562750588892</v>
+        <v>32029215.29184952</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>7522.545642084132</v>
@@ -7438,6 +7499,12 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>9021.195495274076</v>
+      </c>
+      <c r="W10" t="n">
+        <v>115.194398727371</v>
+      </c>
+      <c r="X10" t="n">
+        <v>239.1304876271705</v>
       </c>
     </row>
     <row r="11">
@@ -7456,10 +7523,10 @@
         <v>77.48213071271361</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>44.80214596102493</v>
+        <v>1981.149134072268</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>102.0172235989522</v>
+        <v>451512.3859759013</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>1184.193498826875</v>
@@ -7508,6 +7575,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>1275.963462996302</v>
+      </c>
+      <c r="W11" t="n">
+        <v>44.32874137752759</v>
+      </c>
+      <c r="X11" t="n">
+        <v>100.3757576934664</v>
       </c>
     </row>
     <row r="12">
@@ -7526,10 +7599,10 @@
         <v>60.47920317327088</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>36.07884047162405</v>
+        <v>1285.725322491632</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45.98260971105974</v>
+        <v>3025.478453815313</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>395.8880531253774</v>
@@ -7578,6 +7651,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>405.7840844709587</v>
+      </c>
+      <c r="W12" t="n">
+        <v>35.71921474863613</v>
+      </c>
+      <c r="X12" t="n">
+        <v>45.4727860560026</v>
       </c>
     </row>
     <row r="13">
@@ -7596,10 +7675,10 @@
         <v>105.9540737838667</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>58.89783396730422</v>
+        <v>3420.656848940425</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>94.696301946364</v>
+        <v>525649.2538123906</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>1687.260830089191</v>
@@ -7648,6 +7727,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>1933.149653098989</v>
+      </c>
+      <c r="W13" t="n">
+        <v>58.23096688103647</v>
+      </c>
+      <c r="X13" t="n">
+        <v>93.19774702401548</v>
       </c>
     </row>
     <row r="14">
@@ -7666,10 +7751,10 @@
         <v>57.63885649831866</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>34.59334711335461</v>
+        <v>1182.200226486965</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>74.6502816977321</v>
+        <v>56775.37340919986</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>512.1032894516187</v>
@@ -7718,6 +7803,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>622.0654430531074</v>
+      </c>
+      <c r="W14" t="n">
+        <v>34.25255173466483</v>
+      </c>
+      <c r="X14" t="n">
+        <v>73.57281503821038</v>
       </c>
     </row>
     <row r="15">
@@ -7736,10 +7827,10 @@
         <v>259.279322148687</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>128.7679352494664</v>
+        <v>16306.38643078335</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>481.4906633694268</v>
+        <v>143289060.6835364</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>7900.416310943547</v>
@@ -7788,6 +7879,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>13990.40533945842</v>
+      </c>
+      <c r="W15" t="n">
+        <v>127.0320565197593</v>
+      </c>
+      <c r="X15" t="n">
+        <v>470.4447458749114</v>
       </c>
     </row>
     <row r="16">
@@ -7806,10 +7903,10 @@
         <v>107.2156311313718</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>59.5103419824079</v>
+        <v>3492.048749781905</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>118.5322649776393</v>
+        <v>1035118.278922392</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>1361.395938054995</v>
@@ -7858,6 +7955,12 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>1602.140499612354</v>
+      </c>
+      <c r="W16" t="n">
+        <v>58.83483921363852</v>
+      </c>
+      <c r="X16" t="n">
+        <v>116.5867770529578</v>
       </c>
     </row>
     <row r="17">
@@ -7876,10 +7979,10 @@
         <v>95.34341457700349</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>53.70852769226155</v>
+        <v>2845.346422882955</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>114.1195904507012</v>
+        <v>490526.7828782875</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>569.8461894065326</v>
@@ -7928,6 +8031,12 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>772.8955493412088</v>
+      </c>
+      <c r="W17" t="n">
+        <v>53.11410089441183</v>
+      </c>
+      <c r="X17" t="n">
+        <v>112.2402168821007</v>
       </c>
     </row>
     <row r="18">
@@ -7946,10 +8055,10 @@
         <v>290.4032907845278</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>142.1809802587571</v>
+        <v>19873.63175015984</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>396.5832957514189</v>
+        <v>24636366.7437913</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>3228.620570998742</v>
@@ -7998,6 +8107,12 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>4315.276633604712</v>
+      </c>
+      <c r="W18" t="n">
+        <v>140.2254598404266</v>
+      </c>
+      <c r="X18" t="n">
+        <v>388.4489790223478</v>
       </c>
     </row>
     <row r="19">
@@ -8016,10 +8131,10 @@
         <v>166.1340450683217</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>87.26527673512484</v>
+        <v>7499.053469131032</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>253.8864791671364</v>
+        <v>10067795.4979381</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>1781.28598009776</v>
@@ -8068,6 +8183,12 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>2428.836762865972</v>
+      </c>
+      <c r="W19" t="n">
+        <v>86.18250771615789</v>
+      </c>
+      <c r="X19" t="n">
+        <v>248.7387011216484</v>
       </c>
     </row>
     <row r="20">
@@ -8086,10 +8207,10 @@
         <v>201.4147193620043</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>103.2624399584986</v>
+        <v>10494.3805342664</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>246.3072636307114</v>
+        <v>3053422.756122975</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>1402.335676055655</v>
@@ -8138,6 +8259,12 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>1758.686511539419</v>
+      </c>
+      <c r="W20" t="n">
+        <v>101.9332354274601</v>
+      </c>
+      <c r="X20" t="n">
+        <v>241.6614216340791</v>
       </c>
     </row>
     <row r="21">
@@ -8156,10 +8283,10 @@
         <v>539.0465277017063</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>244.1399999818906</v>
+        <v>58487.6817513493</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>669.4830107372259</v>
+        <v>89769700.66949072</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>10399.7596017777</v>
@@ -8208,6 +8335,12 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>15231.97284803453</v>
+      </c>
+      <c r="W21" t="n">
+        <v>240.4187470028571</v>
+      </c>
+      <c r="X21" t="n">
+        <v>654.8135630424505</v>
       </c>
     </row>
     <row r="22">
@@ -8226,10 +8359,10 @@
         <v>554.842266325365</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>250.3817542347209</v>
+        <v>61511.19550865472</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>650.6425908334182</v>
+        <v>20307429.16303904</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>3230.237663140062</v>
@@ -8278,6 +8411,12 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>4393.486978686482</v>
+      </c>
+      <c r="W22" t="n">
+        <v>246.5479730823474</v>
+      </c>
+      <c r="X22" t="n">
+        <v>636.5676420453372</v>
       </c>
     </row>
     <row r="23">
@@ -8296,10 +8435,10 @@
         <v>342.28011528039</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>164.1469836285015</v>
+        <v>26475.57596605034</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>260.0839283740049</v>
+        <v>257355.8570381914</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1585.623720524716</v>
@@ -8348,6 +8487,12 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>2438.947746756535</v>
+      </c>
+      <c r="W23" t="n">
+        <v>161.8243851182435</v>
+      </c>
+      <c r="X23" t="n">
+        <v>255.6836830337007</v>
       </c>
     </row>
     <row r="24">
@@ -8366,10 +8511,10 @@
         <v>774.1123372933218</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>334.9836815297292</v>
+        <v>109992.0323623284</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>887.5793511915913</v>
+        <v>233163707.6483468</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>14531.04809777599</v>
@@ -8418,6 +8563,12 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>27059.64822683251</v>
+      </c>
+      <c r="W24" t="n">
+        <v>329.5863475118373</v>
+      </c>
+      <c r="X24" t="n">
+        <v>866.9998707232148</v>
       </c>
     </row>
     <row r="25">
@@ -8436,10 +8587,10 @@
         <v>700.024899276907</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>306.7856155696367</v>
+        <v>92281.6346020435</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>959.9020472311886</v>
+        <v>157235608.552394</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>18812.47867781942</v>
@@ -8488,6 +8639,12 @@
       </c>
       <c r="V25" s="2" t="n">
         <v>36288.2726685448</v>
+      </c>
+      <c r="W25" t="n">
+        <v>301.9167771834395</v>
+      </c>
+      <c r="X25" t="n">
+        <v>937.442947901725</v>
       </c>
     </row>
     <row r="26">
@@ -8506,10 +8663,10 @@
         <v>667.1047951632398</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>294.1371646683615</v>
+        <v>84841.43339337071</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>674.4822490822171</v>
+        <v>62527803.44447803</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>9604.557184187423</v>
@@ -8558,6 +8715,12 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>18119.63361450618</v>
+      </c>
+      <c r="W26" t="n">
+        <v>289.5031150051289</v>
+      </c>
+      <c r="X26" t="n">
+        <v>659.6522587098927</v>
       </c>
     </row>
     <row r="27">
@@ -8576,10 +8739,10 @@
         <v>283.8960829203255</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>139.3922948064564</v>
+        <v>19102.99047956023</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>456.8816203995038</v>
+        <v>21093286.41108694</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>10688.37428255109</v>
@@ -8628,6 +8791,12 @@
       </c>
       <c r="V27" s="2" t="n">
         <v>17690.62826767249</v>
+      </c>
+      <c r="W27" t="n">
+        <v>137.4827375072899</v>
+      </c>
+      <c r="X27" t="n">
+        <v>446.9845314950023</v>
       </c>
     </row>
     <row r="28">
@@ -8646,10 +8815,10 @@
         <v>158.5523351163148</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>83.7741522198167</v>
+        <v>6912.013677141386</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>197.0827762362635</v>
+        <v>2905118.284101523</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>3502.459341143938</v>
@@ -8698,6 +8867,12 @@
       </c>
       <c r="V28" s="2" t="n">
         <v>5115.038689195876</v>
+      </c>
+      <c r="W28" t="n">
+        <v>82.7441380903153</v>
+      </c>
+      <c r="X28" t="n">
+        <v>193.4161451236454</v>
       </c>
     </row>
     <row r="29">
@@ -8716,10 +8891,10 @@
         <v>170.5183408315064</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>89.27490104962962</v>
+        <v>7847.805849559743</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>176.9373943907212</v>
+        <v>421935.6503426669</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>1050.872908400935</v>
@@ -8768,6 +8943,12 @@
       </c>
       <c r="V29" s="2" t="n">
         <v>1775.112324617013</v>
+      </c>
+      <c r="W29" t="n">
+        <v>88.1615890100929</v>
+      </c>
+      <c r="X29" t="n">
+        <v>173.8688131652051</v>
       </c>
     </row>
     <row r="30">
@@ -8786,10 +8967,10 @@
         <v>33.25478525090308</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>21.38999140408276</v>
+        <v>452.7362805178933</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>53.3543341036877</v>
+        <v>34182.13293954706</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>151.0840559857222</v>
@@ -8838,6 +9019,12 @@
       </c>
       <c r="V30" s="2" t="n">
         <v>184.933078657571</v>
+      </c>
+      <c r="W30" t="n">
+        <v>21.20773331913684</v>
+      </c>
+      <c r="X30" t="n">
+        <v>52.60142902442914</v>
       </c>
     </row>
     <row r="31">
@@ -8856,10 +9043,10 @@
         <v>20.60629913270001</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>14.07767872356361</v>
+        <v>196.3862851317653</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>22.7155424150044</v>
+        <v>1009.116171699102</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>131.7107200374602</v>
@@ -8908,6 +9095,12 @@
       </c>
       <c r="V31" s="2" t="n">
         <v>136.520004315677</v>
+      </c>
+      <c r="W31" t="n">
+        <v>13.9740493131894</v>
+      </c>
+      <c r="X31" t="n">
+        <v>22.49014080431145</v>
       </c>
     </row>
     <row r="32">
@@ -8926,10 +9119,10 @@
         <v>39.81071705534973</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>25.03316360818054</v>
+        <v>619.755778182163</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>36.58982244759314</v>
+        <v>1877.598068216403</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>741.6294947655872</v>
@@ -8978,6 +9171,12 @@
       </c>
       <c r="V32" s="2" t="n">
         <v>765.5198801150671</v>
+      </c>
+      <c r="W32" t="n">
+        <v>24.80895948012596</v>
+      </c>
+      <c r="X32" t="n">
+        <v>36.19733500412019</v>
       </c>
     </row>
     <row r="33">
@@ -8996,10 +9195,10 @@
         <v>14.71217112194568</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>10.48658207174712</v>
+        <v>109.0829669303666</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>17.347997652967</v>
+        <v>1554.089563973466</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>87.52377751878464</v>
@@ -9048,6 +9247,12 @@
       </c>
       <c r="V33" s="2" t="n">
         <v>96.44722636844091</v>
+      </c>
+      <c r="W33" t="n">
+        <v>10.41795560111873</v>
+      </c>
+      <c r="X33" t="n">
+        <v>17.17468947042643</v>
       </c>
     </row>
     <row r="34">
@@ -9066,10 +9271,10 @@
         <v>15.8129952840593</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>11.16927777058033</v>
+        <v>123.7214437349237</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>22.58093904322016</v>
+        <v>7384.919422723911</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>110.7651612284971</v>
@@ -9118,6 +9323,12 @@
       </c>
       <c r="V34" s="2" t="n">
         <v>118.9310592810974</v>
+      </c>
+      <c r="W34" t="n">
+        <v>11.09422854051634</v>
+      </c>
+      <c r="X34" t="n">
+        <v>22.31576842467771</v>
       </c>
     </row>
     <row r="35">
@@ -9136,10 +9347,10 @@
         <v>18.61708723298875</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>12.88233877030954</v>
+        <v>164.501950637208</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>42.22089816890895</v>
+        <v>16631.86282478124</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>603.9895006722445</v>
@@ -9188,6 +9399,12 @@
       </c>
       <c r="V35" s="2" t="n">
         <v>1135.088390380274</v>
+      </c>
+      <c r="W35" t="n">
+        <v>12.79067902832161</v>
+      </c>
+      <c r="X35" t="n">
+        <v>41.60617018264662</v>
       </c>
     </row>
     <row r="36">
@@ -9206,10 +9423,10 @@
         <v>10</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>7.482941260344036</v>
+        <v>55.60807552276464</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>7.482941260344036</v>
+        <v>55.60807552276464</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>3.508771929824562</v>
@@ -9258,6 +9475,12 @@
       </c>
       <c r="V36" s="2" t="n">
         <v>3.409847954707133</v>
+      </c>
+      <c r="W36" t="n">
+        <v>7.440983535989962</v>
+      </c>
+      <c r="X36" t="n">
+        <v>7.440983535989962</v>
       </c>
     </row>
     <row r="37">
@@ -9276,10 +9499,10 @@
         <v>103.7909360953987</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>57.84544707318343</v>
+        <v>3299.71295534195</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>56.93258709702179</v>
+        <v>5979.611909703869</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>468.918007812782</v>
@@ -9328,6 +9551,12 @@
       </c>
       <c r="V37" s="2" t="n">
         <v>756.8536318254826</v>
+      </c>
+      <c r="W37" t="n">
+        <v>57.19337639860824</v>
+      </c>
+      <c r="X37" t="n">
+        <v>56.26029517977418</v>
       </c>
     </row>
     <row r="38">
@@ -9346,10 +9575,10 @@
         <v>10</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>7.482941260344036</v>
+        <v>55.60807552276464</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>7.482941260344036</v>
+        <v>55.60807552276464</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>115.384615384615</v>
@@ -9398,6 +9627,12 @@
       </c>
       <c r="V38" s="2" t="n">
         <v>116.84699322354</v>
+      </c>
+      <c r="W38" t="n">
+        <v>7.440983535989962</v>
+      </c>
+      <c r="X38" t="n">
+        <v>7.440983535989961</v>
       </c>
     </row>
     <row r="39">
@@ -9469,6 +9704,12 @@
       <c r="V39" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W39" t="n">
+        <v>1</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -9537,6 +9778,12 @@
         <v>1</v>
       </c>
       <c r="V40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9551,7 +9798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:X40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9689,6 +9936,16 @@
           <t>MC_new_TE_EEfix</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -9738,19 +9995,22 @@
       <c r="O2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9823,6 +10083,12 @@
       <c r="V3" s="2" t="n">
         <v>0.9810424917673825</v>
       </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -9840,10 +10106,10 @@
         <v>92.36817646243769</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>52.24066894619853</v>
+        <v>2692.201195451597</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>644.4329212894243</v>
+        <v>529081636.8323154</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>94248.91488281998</v>
@@ -9892,6 +10158,12 @@
       </c>
       <c r="V4" s="2" t="n">
         <v>171169.8746666788</v>
+      </c>
+      <c r="W4" t="n">
+        <v>51.66648764020988</v>
+      </c>
+      <c r="X4" t="n">
+        <v>627.7811065825483</v>
       </c>
     </row>
     <row r="5">
@@ -9910,10 +10182,10 @@
         <v>804.9195518555838</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>346.6074198764927</v>
+        <v>117743.9698590211</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>889.0690031283369</v>
+        <v>272480122.5285062</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>1874464.079650443</v>
@@ -9962,6 +10234,12 @@
       </c>
       <c r="V5" s="2" t="n">
         <v>2858734.731157274</v>
+      </c>
+      <c r="W5" t="n">
+        <v>340.9903037368433</v>
+      </c>
+      <c r="X5" t="n">
+        <v>868.769579273888</v>
       </c>
     </row>
     <row r="6">
@@ -9980,10 +10258,10 @@
         <v>1309.957766003465</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>530.5280675169544</v>
+        <v>275450.6106944028</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1251.989192473138</v>
+        <v>174871731.5548666</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>529369.1988808451</v>
@@ -10032,6 +10310,12 @@
       </c>
       <c r="V6" s="2" t="n">
         <v>754975.0603875497</v>
+      </c>
+      <c r="W6" t="n">
+        <v>521.3099884589022</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1222.744857278365</v>
       </c>
     </row>
     <row r="7">
@@ -10050,10 +10334,10 @@
         <v>252.7372954965662</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>125.9235032748216</v>
+        <v>15595.1383676661</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>559.5202679373864</v>
+        <v>25661835.79016795</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>114992570.5967543</v>
@@ -10102,6 +10386,12 @@
       </c>
       <c r="V7" s="2" t="n">
         <v>152627302.111988</v>
+      </c>
+      <c r="W7" t="n">
+        <v>124.2337220943735</v>
+      </c>
+      <c r="X7" t="n">
+        <v>547.0691242980095</v>
       </c>
     </row>
     <row r="8">
@@ -10120,10 +10410,10 @@
         <v>908.9880051560747</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>385.4728863525418</v>
+        <v>145576.6960244619</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>784.4685456782904</v>
+        <v>48080410.42140355</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>125208.7929524061</v>
@@ -10172,6 +10462,12 @@
       </c>
       <c r="V8" s="2" t="n">
         <v>183923.261916347</v>
+      </c>
+      <c r="W8" t="n">
+        <v>379.1133335324108</v>
+      </c>
+      <c r="X8" t="n">
+        <v>767.7179194002755</v>
       </c>
     </row>
     <row r="9">
@@ -10190,10 +10486,10 @@
         <v>308.6860101337908</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>149.9746627449809</v>
+        <v>22108.04252509096</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>602.3668038671244</v>
+        <v>195781560.0391699</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>10706.10148649219</v>
@@ -10242,6 +10538,12 @@
       </c>
       <c r="V9" s="2" t="n">
         <v>20404.47103668627</v>
+      </c>
+      <c r="W9" t="n">
+        <v>147.8898989820327</v>
+      </c>
+      <c r="X9" t="n">
+        <v>588.1973200515148</v>
       </c>
     </row>
     <row r="10">
@@ -10260,10 +10562,10 @@
         <v>231.7551372376293</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>116.7365209876158</v>
+        <v>13406.0954074146</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>243.5562750588892</v>
+        <v>32029215.29184952</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>7522.545642084132</v>
@@ -10312,6 +10614,12 @@
       </c>
       <c r="V10" s="2" t="n">
         <v>9021.195495274076</v>
+      </c>
+      <c r="W10" t="n">
+        <v>115.194398727371</v>
+      </c>
+      <c r="X10" t="n">
+        <v>239.1304876271705</v>
       </c>
     </row>
     <row r="11">
@@ -10330,10 +10638,10 @@
         <v>77.48213071271361</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>44.80214596102493</v>
+        <v>1981.149134072268</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>102.0172235989522</v>
+        <v>451512.3859759013</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>1184.193498826875</v>
@@ -10382,6 +10690,12 @@
       </c>
       <c r="V11" s="2" t="n">
         <v>1275.963462996302</v>
+      </c>
+      <c r="W11" t="n">
+        <v>44.32874137752759</v>
+      </c>
+      <c r="X11" t="n">
+        <v>100.3757576934664</v>
       </c>
     </row>
     <row r="12">
@@ -10400,10 +10714,10 @@
         <v>60.47920317327088</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>36.07884047162405</v>
+        <v>1285.725322491632</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>45.98260971105974</v>
+        <v>3025.478453815313</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>395.8880531253774</v>
@@ -10452,6 +10766,12 @@
       </c>
       <c r="V12" s="2" t="n">
         <v>405.7840844709587</v>
+      </c>
+      <c r="W12" t="n">
+        <v>35.71921474863613</v>
+      </c>
+      <c r="X12" t="n">
+        <v>45.4727860560026</v>
       </c>
     </row>
     <row r="13">
@@ -10470,10 +10790,10 @@
         <v>105.9540737838667</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>58.89783396730422</v>
+        <v>3420.656848940425</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>94.696301946364</v>
+        <v>525649.2538123906</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>1687.260830089191</v>
@@ -10522,6 +10842,12 @@
       </c>
       <c r="V13" s="2" t="n">
         <v>1933.149653098989</v>
+      </c>
+      <c r="W13" t="n">
+        <v>58.23096688103647</v>
+      </c>
+      <c r="X13" t="n">
+        <v>93.19774702401548</v>
       </c>
     </row>
     <row r="14">
@@ -10540,10 +10866,10 @@
         <v>57.63885649831866</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>34.59334711335461</v>
+        <v>1182.200226486965</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>74.6502816977321</v>
+        <v>56775.37340919986</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>512.1032894516187</v>
@@ -10592,6 +10918,12 @@
       </c>
       <c r="V14" s="2" t="n">
         <v>622.0654430531074</v>
+      </c>
+      <c r="W14" t="n">
+        <v>34.25255173466483</v>
+      </c>
+      <c r="X14" t="n">
+        <v>73.57281503821038</v>
       </c>
     </row>
     <row r="15">
@@ -10610,10 +10942,10 @@
         <v>259.279322148687</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>128.7679352494664</v>
+        <v>16306.38643078335</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>481.4906633694268</v>
+        <v>143289060.6835364</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>7900.416310943547</v>
@@ -10662,6 +10994,12 @@
       </c>
       <c r="V15" s="2" t="n">
         <v>13990.40533945842</v>
+      </c>
+      <c r="W15" t="n">
+        <v>127.0320565197593</v>
+      </c>
+      <c r="X15" t="n">
+        <v>470.4447458749114</v>
       </c>
     </row>
     <row r="16">
@@ -10680,10 +11018,10 @@
         <v>107.2156311313718</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>59.5103419824079</v>
+        <v>3492.048749781905</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>118.5322649776393</v>
+        <v>1035118.278922392</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>1361.395938054995</v>
@@ -10732,6 +11070,12 @@
       </c>
       <c r="V16" s="2" t="n">
         <v>1602.140499612354</v>
+      </c>
+      <c r="W16" t="n">
+        <v>58.83483921363852</v>
+      </c>
+      <c r="X16" t="n">
+        <v>116.5867770529578</v>
       </c>
     </row>
     <row r="17">
@@ -10750,10 +11094,10 @@
         <v>95.34341457700349</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>53.70852769226155</v>
+        <v>2845.346422882955</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>114.1195904507012</v>
+        <v>490526.7828782875</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>569.8461894065326</v>
@@ -10802,6 +11146,12 @@
       </c>
       <c r="V17" s="2" t="n">
         <v>772.8955493412088</v>
+      </c>
+      <c r="W17" t="n">
+        <v>53.11410089441183</v>
+      </c>
+      <c r="X17" t="n">
+        <v>112.2402168821007</v>
       </c>
     </row>
     <row r="18">
@@ -10820,10 +11170,10 @@
         <v>290.4032907845278</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>142.1809802587571</v>
+        <v>19873.63175015984</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>396.5832957514189</v>
+        <v>24636366.7437913</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>3228.620570998742</v>
@@ -10872,6 +11222,12 @@
       </c>
       <c r="V18" s="2" t="n">
         <v>4315.276633604712</v>
+      </c>
+      <c r="W18" t="n">
+        <v>140.2254598404266</v>
+      </c>
+      <c r="X18" t="n">
+        <v>388.4489790223478</v>
       </c>
     </row>
     <row r="19">
@@ -10890,10 +11246,10 @@
         <v>166.1340450683217</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>87.26527673512484</v>
+        <v>7499.053469131032</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>253.8864791671364</v>
+        <v>10067795.4979381</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>1781.28598009776</v>
@@ -10942,6 +11298,12 @@
       </c>
       <c r="V19" s="2" t="n">
         <v>2428.836762865972</v>
+      </c>
+      <c r="W19" t="n">
+        <v>86.18250771615789</v>
+      </c>
+      <c r="X19" t="n">
+        <v>248.7387011216484</v>
       </c>
     </row>
     <row r="20">
@@ -10960,10 +11322,10 @@
         <v>201.4147193620043</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>103.2624399584986</v>
+        <v>10494.3805342664</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>246.3072636307114</v>
+        <v>3053422.756122975</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>1402.335676055655</v>
@@ -11012,6 +11374,12 @@
       </c>
       <c r="V20" s="2" t="n">
         <v>1758.686511539419</v>
+      </c>
+      <c r="W20" t="n">
+        <v>101.9332354274601</v>
+      </c>
+      <c r="X20" t="n">
+        <v>241.6614216340791</v>
       </c>
     </row>
     <row r="21">
@@ -11030,10 +11398,10 @@
         <v>539.0465277017063</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>244.1399999818906</v>
+        <v>58487.6817513493</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>669.4830107372259</v>
+        <v>89769700.66949072</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>10399.7596017777</v>
@@ -11082,6 +11450,12 @@
       </c>
       <c r="V21" s="2" t="n">
         <v>15231.97284803453</v>
+      </c>
+      <c r="W21" t="n">
+        <v>240.4187470028571</v>
+      </c>
+      <c r="X21" t="n">
+        <v>654.8135630424505</v>
       </c>
     </row>
     <row r="22">
@@ -11100,10 +11474,10 @@
         <v>554.842266325365</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>250.3817542347209</v>
+        <v>61511.19550865472</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>650.6425908334182</v>
+        <v>20307429.16303904</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>3230.237663140062</v>
@@ -11152,6 +11526,12 @@
       </c>
       <c r="V22" s="2" t="n">
         <v>4393.486978686482</v>
+      </c>
+      <c r="W22" t="n">
+        <v>246.5479730823474</v>
+      </c>
+      <c r="X22" t="n">
+        <v>636.5676420453372</v>
       </c>
     </row>
     <row r="23">
@@ -11170,10 +11550,10 @@
         <v>342.28011528039</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>164.1469836285015</v>
+        <v>26475.57596605034</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>260.0839283740049</v>
+        <v>257355.8570381914</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>1585.623720524716</v>
@@ -11222,6 +11602,12 @@
       </c>
       <c r="V23" s="2" t="n">
         <v>2438.947746756535</v>
+      </c>
+      <c r="W23" t="n">
+        <v>161.8243851182435</v>
+      </c>
+      <c r="X23" t="n">
+        <v>255.6836830337007</v>
       </c>
     </row>
     <row r="24">
@@ -11240,10 +11626,10 @@
         <v>774.1123372933218</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>334.9836815297292</v>
+        <v>109992.0323623284</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>887.5793511915913</v>
+        <v>233163707.6483468</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>14531.04809777599</v>
@@ -11292,6 +11678,12 @@
       </c>
       <c r="V24" s="2" t="n">
         <v>27059.64822683251</v>
+      </c>
+      <c r="W24" t="n">
+        <v>329.5863475118373</v>
+      </c>
+      <c r="X24" t="n">
+        <v>866.9998707232148</v>
       </c>
     </row>
     <row r="25">
@@ -11310,10 +11702,10 @@
         <v>700.024899276907</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>306.7856155696367</v>
+        <v>92281.6346020435</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>959.9020472311886</v>
+        <v>157235608.552394</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>18812.47867781942</v>
@@ -11362,6 +11754,12 @@
       </c>
       <c r="V25" s="2" t="n">
         <v>36288.2726685448</v>
+      </c>
+      <c r="W25" t="n">
+        <v>301.9167771834395</v>
+      </c>
+      <c r="X25" t="n">
+        <v>937.442947901725</v>
       </c>
     </row>
     <row r="26">
@@ -11380,10 +11778,10 @@
         <v>667.1047951632398</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>294.1371646683615</v>
+        <v>84841.43339337071</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>674.4822490822171</v>
+        <v>62527803.44447803</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>9604.557184187423</v>
@@ -11432,6 +11830,12 @@
       </c>
       <c r="V26" s="2" t="n">
         <v>18119.63361450618</v>
+      </c>
+      <c r="W26" t="n">
+        <v>289.5031150051289</v>
+      </c>
+      <c r="X26" t="n">
+        <v>659.6522587098927</v>
       </c>
     </row>
     <row r="27">
@@ -11450,10 +11854,10 @@
         <v>283.8960829203255</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>139.3922948064564</v>
+        <v>19102.99047956023</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>456.8816203995038</v>
+        <v>21093286.41108694</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>10688.37428255109</v>
@@ -11502,6 +11906,12 @@
       </c>
       <c r="V27" s="2" t="n">
         <v>17690.62826767249</v>
+      </c>
+      <c r="W27" t="n">
+        <v>137.4827375072899</v>
+      </c>
+      <c r="X27" t="n">
+        <v>446.9845314950023</v>
       </c>
     </row>
     <row r="28">
@@ -11520,10 +11930,10 @@
         <v>158.5523351163148</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>83.7741522198167</v>
+        <v>6912.013677141386</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>197.0827762362635</v>
+        <v>2905118.284101523</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>3502.459341143938</v>
@@ -11572,6 +11982,12 @@
       </c>
       <c r="V28" s="2" t="n">
         <v>5115.038689195876</v>
+      </c>
+      <c r="W28" t="n">
+        <v>82.7441380903153</v>
+      </c>
+      <c r="X28" t="n">
+        <v>193.4161451236454</v>
       </c>
     </row>
     <row r="29">
@@ -11590,10 +12006,10 @@
         <v>170.5183408315064</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>89.27490104962962</v>
+        <v>7847.805849559743</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>176.9373943907212</v>
+        <v>421935.6503426669</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>1050.872908400935</v>
@@ -11642,6 +12058,12 @@
       </c>
       <c r="V29" s="2" t="n">
         <v>1775.112324617013</v>
+      </c>
+      <c r="W29" t="n">
+        <v>88.1615890100929</v>
+      </c>
+      <c r="X29" t="n">
+        <v>173.8688131652051</v>
       </c>
     </row>
     <row r="30">
@@ -11660,10 +12082,10 @@
         <v>33.25478525090308</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>21.38999140408276</v>
+        <v>452.7362805178933</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>53.3543341036877</v>
+        <v>34182.13293954706</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>151.0840559857222</v>
@@ -11712,6 +12134,12 @@
       </c>
       <c r="V30" s="2" t="n">
         <v>184.933078657571</v>
+      </c>
+      <c r="W30" t="n">
+        <v>21.20773331913684</v>
+      </c>
+      <c r="X30" t="n">
+        <v>52.60142902442914</v>
       </c>
     </row>
     <row r="31">
@@ -11730,10 +12158,10 @@
         <v>20.60629913270001</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>14.07767872356361</v>
+        <v>196.3862851317653</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>22.7155424150044</v>
+        <v>1009.116171699102</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>131.7107200374602</v>
@@ -11782,6 +12210,12 @@
       </c>
       <c r="V31" s="2" t="n">
         <v>136.520004315677</v>
+      </c>
+      <c r="W31" t="n">
+        <v>13.9740493131894</v>
+      </c>
+      <c r="X31" t="n">
+        <v>22.49014080431145</v>
       </c>
     </row>
     <row r="32">
@@ -11800,10 +12234,10 @@
         <v>39.81071705534973</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>25.03316360818054</v>
+        <v>619.755778182163</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>36.58982244759314</v>
+        <v>1877.598068216403</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>741.6294947655872</v>
@@ -11852,6 +12286,12 @@
       </c>
       <c r="V32" s="2" t="n">
         <v>765.5198801150671</v>
+      </c>
+      <c r="W32" t="n">
+        <v>24.80895948012596</v>
+      </c>
+      <c r="X32" t="n">
+        <v>36.19733500412019</v>
       </c>
     </row>
     <row r="33">
@@ -11870,10 +12310,10 @@
         <v>14.71217112194568</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>10.48658207174712</v>
+        <v>109.0829669303666</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>17.347997652967</v>
+        <v>1554.089563973466</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>87.52377751878464</v>
@@ -11922,6 +12362,12 @@
       </c>
       <c r="V33" s="2" t="n">
         <v>96.44722636844091</v>
+      </c>
+      <c r="W33" t="n">
+        <v>10.41795560111873</v>
+      </c>
+      <c r="X33" t="n">
+        <v>17.17468947042643</v>
       </c>
     </row>
     <row r="34">
@@ -11940,10 +12386,10 @@
         <v>15.8129952840593</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>11.16927777058033</v>
+        <v>123.7214437349237</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>22.58093904322016</v>
+        <v>7384.919422723911</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>110.7651612284971</v>
@@ -11992,6 +12438,12 @@
       </c>
       <c r="V34" s="2" t="n">
         <v>118.9310592810974</v>
+      </c>
+      <c r="W34" t="n">
+        <v>11.09422854051634</v>
+      </c>
+      <c r="X34" t="n">
+        <v>22.31576842467771</v>
       </c>
     </row>
     <row r="35">
@@ -12010,10 +12462,10 @@
         <v>18.61708723298875</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>12.88233877030954</v>
+        <v>164.501950637208</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>42.22089816890895</v>
+        <v>16631.86282478124</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>603.9895006722445</v>
@@ -12062,6 +12514,12 @@
       </c>
       <c r="V35" s="2" t="n">
         <v>1135.088390380274</v>
+      </c>
+      <c r="W35" t="n">
+        <v>12.79067902832161</v>
+      </c>
+      <c r="X35" t="n">
+        <v>41.60617018264662</v>
       </c>
     </row>
     <row r="36">
@@ -12080,10 +12538,10 @@
         <v>10</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>7.482941260344036</v>
+        <v>55.60807552276464</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>7.482941260344036</v>
+        <v>55.60807552276464</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>3.508771929824562</v>
@@ -12132,6 +12590,12 @@
       </c>
       <c r="V36" s="2" t="n">
         <v>3.409847954707133</v>
+      </c>
+      <c r="W36" t="n">
+        <v>7.440983535989962</v>
+      </c>
+      <c r="X36" t="n">
+        <v>7.440983535989962</v>
       </c>
     </row>
     <row r="37">
@@ -12150,10 +12614,10 @@
         <v>103.7909360953987</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>57.84544707318343</v>
+        <v>3299.71295534195</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>56.93258709702179</v>
+        <v>5979.611909703869</v>
       </c>
       <c r="G37" s="2" t="n">
         <v>468.918007812782</v>
@@ -12202,6 +12666,12 @@
       </c>
       <c r="V37" s="2" t="n">
         <v>756.8536318254826</v>
+      </c>
+      <c r="W37" t="n">
+        <v>57.19337639860824</v>
+      </c>
+      <c r="X37" t="n">
+        <v>56.26029517977418</v>
       </c>
     </row>
     <row r="38">
@@ -12220,10 +12690,10 @@
         <v>10</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>7.482941260344036</v>
+        <v>55.60807552276464</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>7.482941260344036</v>
+        <v>55.60807552276464</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>115.384615384615</v>
@@ -12272,6 +12742,12 @@
       </c>
       <c r="V38" s="2" t="n">
         <v>116.84699322354</v>
+      </c>
+      <c r="W38" t="n">
+        <v>7.440983535989962</v>
+      </c>
+      <c r="X38" t="n">
+        <v>7.440983535989961</v>
       </c>
     </row>
     <row r="39">
@@ -12343,6 +12819,12 @@
       <c r="V39" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="W39" t="n">
+        <v>1</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -12411,6 +12893,12 @@
         <v>1</v>
       </c>
       <c r="V40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12883,7 +13371,6 @@
           <t>WARN</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr"/>
       <c r="AD2" s="2" t="n">
         <v>0.01631263510340195</v>
       </c>
@@ -13009,7 +13496,6 @@
       <c r="H3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>South_China_Sea_SCS-2007_Northern_South_China_Sea (1970s)</t>
@@ -13073,7 +13559,6 @@
           <t>WARN</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
       <c r="AD3" s="2" t="n">
         <v>0</v>
       </c>
@@ -13267,7 +13752,6 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
       <c r="AD4" s="2" t="n">
         <v>0.01651691203182949</v>
       </c>
@@ -13369,7 +13853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -13430,14 +13914,12 @@
       <c r="C2" s="2" t="n">
         <v>119.8248955418437</v>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" s="2" t="n">
         <v>130696.17</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0.0009168202522066536</v>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -13451,14 +13933,12 @@
       <c r="C3" s="2" t="n">
         <v>189.2958944147165</v>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" s="2" t="n">
         <v>130696.17</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>0.001448366041749475</v>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -13467,19 +13947,17 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>91.8611515580328</v>
+        <v>16255.1469396623</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>91.8611515580328</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>16255.1469396623</v>
+      </c>
       <c r="E4" s="2" t="n">
         <v>130696.17</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.0007028603176208821</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>0.1243735523364021</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -13488,22 +13966,22 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>238.2994096038377</v>
+        <v>33116296.38146015</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>238.2994096038377</v>
+        <v>33116296.38146015</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>114.6402648958329</v>
+        <v>19185462.1483394</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>130696.17</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.001823308285191813</v>
+        <v>253.3838319933947</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.0008771509134187555</v>
+        <v>146.7943716203727</v>
       </c>
     </row>
     <row r="6">
@@ -13904,6 +14382,50 @@
       </c>
       <c r="G21" s="2" t="n">
         <v>0.03780426147950598</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>90.59129514388292</v>
+      </c>
+      <c r="C22" t="n">
+        <v>90.59129514388292</v>
+      </c>
+      <c r="E22" t="n">
+        <v>130696.17</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.0006931442225421213</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>233.3084162749475</v>
+      </c>
+      <c r="C23" t="n">
+        <v>233.3084162749475</v>
+      </c>
+      <c r="D23" t="n">
+        <v>112.249129033277</v>
+      </c>
+      <c r="E23" t="n">
+        <v>130696.17</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.001785120530119188</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0008588555351949255</v>
       </c>
     </row>
   </sheetData>
@@ -14039,7 +14561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -14075,7 +14597,6 @@
           <t>NaN means not available, never zero. A basal source a method does not resolve is NaN, and a method that raised leaves its entire block NaN.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -14088,7 +14609,6 @@
           <t>sppr_all, sppr_inner and sppr_PP are the same table under three source scopes, mirroring get_PPR: sppr_all sums every basal source, sppr_inner drops Import, and sppr_PP drops Import and Detritus. Each is a flat groups x methods table -- rows are group seq with the group name in the first column, one column per method, no MultiIndex. Sums are taken over each method's own basal-source columns before aggregation; the per-source breakdown itself is not written to the workbook.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -14101,7 +14621,6 @@
           <t>SPPR_1986 and SPPR_1995 return one un-attributed SPPR column, so their value cannot be split into a PP-only part: they are NaN in sppr_PP (and in ppr_pp_only) while sppr_inner and sppr_all carry the total. A method that resolves no Detritus source (SPPR_2015) has sppr_inner equal to sppr_PP by construction.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -14114,7 +14633,6 @@
           <t>SPPR_2015() has no only_pp_det parameter (only_pp belongs to get_PPR / get_PPR2NPP_ratio). It is called bare here and PP-only filtering is applied downstream at the get_PPR layer, which is what the ppr_pp_only column and SUM_PP already do.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -14127,7 +14645,6 @@
           <t>Under det_open_mode='none' det_theta does not affect the recycling gain b at all (verified: identical b at theta = 1, 3 and 10). Do not read the health sheet as a theta sensitivity.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -14140,7 +14657,6 @@
           <t>MC runs use exclude_diverged=True, so draws graded FAIL on divergence are dropped as well as draws with a negative SPPR. The two are often the same draws rather than additive -- see the mc_diagnostics sheet for the split by cause.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -14153,7 +14669,6 @@
           <t>SPPR_EwE and the Monte-Carlo methods are called with silent=True rather than silent=False: PPRCalculator imports tqdm.notebook, whose bar needs ipywidgets and raises ImportError('IProgress not found') outside Jupyter, which makes those methods fail outright in a terminal run. Nothing is lost -- this exporter has its own progress bar, and the MC rejection counts appear in mc_diagnostics and in the run report.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -14166,7 +14681,6 @@
           <t>diagnose_sppr grades a CONFIGURATION, not a model: a model can be healthy under one TE_option and divergent under another. Read each row with its config_ columns.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -14179,7 +14693,6 @@
           <t>Every SPPR method, and every diagnose_sppr row, runs in a worker process with a wall-clock budget (180 s by default; --timeout SECONDS on the command line, method_timeout= from Python, and None or 0 to disable it). A method still running when the budget expires is killed and left NaN, exactly like a method that raised -- the status column of this sheet and the run report are the only places that say which of the two happened. A timeout is a statement about this machine and this model, not about the method: rerun it with a larger budget before reading anything into it.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -14223,7 +14736,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'.</t>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer consumption weights.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -14240,7 +14753,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nullspace form of the EwE path sum, global TE at the true mean (Jensen-able on TL).</t>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer consumption-weighted arithmetic mean (Jensen-able on TL).</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -14516,6 +15029,40 @@
         </is>
       </c>
       <c r="C30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>method: SPPR_1995_TEmean_catch</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pauly &amp; Christensen (1995): per-group TE^(1-TL) with global_TE='mean'. Arithmetic mean with consumer catch weights. Consumer biomass fallback when consumer catch is zero.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>method: Ulanowicz_globalTEmean_catch</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nullspace form of the EwE path sum, global TE at the consumer catch-weighted arithmetic mean. Consumer biomass fallback when consumer catch is zero (Jensen-able on TL).</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
